--- a/golden_set/protocol_annotations/P-33_annotation.xlsx
+++ b/golden_set/protocol_annotations/P-33_annotation.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +41,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +72,18 @@
         <bgColor rgb="00FFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -74,11 +97,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,9 +473,12 @@
   </sheetPr>
   <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ANNOTATION INSTRUCTIONS</t>
         </is>
@@ -585,47 +615,47 @@
   <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>section_number</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>extracted_title</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>extracted_page</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>is_correct (Y/N)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>correct_title</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>correct_page</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -645,7 +675,11 @@
       <c r="C2" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
@@ -664,7 +698,11 @@
       <c r="C3" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -683,7 +721,11 @@
       <c r="C4" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
@@ -702,10 +744,18 @@
       <c r="C5" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 26 (offset from 29)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -721,7 +771,11 @@
       <c r="C6" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
@@ -740,7 +794,11 @@
       <c r="C7" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
@@ -759,7 +817,11 @@
       <c r="C8" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
@@ -778,7 +840,11 @@
       <c r="C9" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
@@ -797,7 +863,11 @@
       <c r="C10" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="D10" s="3" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
@@ -816,10 +886,18 @@
       <c r="C11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 2 (offset from 7)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -835,7 +913,11 @@
       <c r="C12" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="D12" s="3" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
@@ -854,10 +936,18 @@
       <c r="C13" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="D13" s="3" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 12 (offset from 17)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -873,10 +963,18 @@
       <c r="C14" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D14" s="3" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 23 (offset from 25)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -892,7 +990,11 @@
       <c r="C15" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
@@ -911,10 +1013,18 @@
       <c r="C16" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="3" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 20 (offset from 25)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -930,7 +1040,11 @@
       <c r="C17" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="D17" s="3" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
@@ -949,10 +1063,18 @@
       <c r="C18" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 2 (offset from 6)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -968,7 +1090,11 @@
       <c r="C19" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
@@ -987,7 +1113,11 @@
       <c r="C20" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
@@ -1006,7 +1136,11 @@
       <c r="C21" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="D21" s="3" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
@@ -1025,10 +1159,18 @@
       <c r="C22" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 9 (offset from 14)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1044,7 +1186,11 @@
       <c r="C23" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="D23" s="3" t="n"/>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
@@ -1063,7 +1209,11 @@
       <c r="C24" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="3" t="n"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
@@ -1082,7 +1232,11 @@
       <c r="C25" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
@@ -1101,10 +1255,18 @@
       <c r="C26" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 82 (offset from 83)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -1120,10 +1282,18 @@
       <c r="C27" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="D27" s="3" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 80 (offset from 83)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1139,7 +1309,11 @@
       <c r="C28" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
@@ -1158,7 +1332,11 @@
       <c r="C29" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="D29" s="3" t="n"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
@@ -1177,7 +1355,11 @@
       <c r="C30" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
@@ -1196,10 +1378,18 @@
       <c r="C31" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="D31" s="3" t="n"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 12 (offset from 17)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1215,10 +1405,18 @@
       <c r="C32" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="D32" s="3" t="n"/>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 16 (offset from 21)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -1234,7 +1432,11 @@
       <c r="C33" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="D33" s="3" t="n"/>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -1253,7 +1455,11 @@
       <c r="C34" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="D34" s="3" t="n"/>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
@@ -1272,7 +1478,11 @@
       <c r="C35" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="n"/>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
@@ -1291,10 +1501,18 @@
       <c r="C36" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D36" s="3" t="n"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 3 (offset from 8)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1310,10 +1528,18 @@
       <c r="C37" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="3" t="n"/>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 3 (offset from 8)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1329,7 +1555,11 @@
       <c r="C38" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
@@ -1348,7 +1578,11 @@
       <c r="C39" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D39" s="3" t="n"/>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
@@ -1367,7 +1601,11 @@
       <c r="C40" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D40" s="3" t="n"/>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
@@ -1386,7 +1624,11 @@
       <c r="C41" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D41" s="3" t="n"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
@@ -1405,10 +1647,18 @@
       <c r="C42" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="D42" s="3" t="n"/>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 85 (offset from 87)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1424,7 +1674,11 @@
       <c r="C43" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="D43" s="3" t="n"/>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
@@ -1443,7 +1697,11 @@
       <c r="C44" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D44" s="3" t="n"/>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>
@@ -1462,10 +1720,18 @@
       <c r="C45" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="D45" s="3" t="n"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 27 (offset from 29)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1481,10 +1747,18 @@
       <c r="C46" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="D46" s="3" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 82 (offset from 85)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1500,10 +1774,18 @@
       <c r="C47" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="D47" s="3" t="n"/>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 82 (offset from 85)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1519,10 +1801,18 @@
       <c r="C48" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D48" s="3" t="n"/>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 3 (offset from 8)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -1538,10 +1828,18 @@
       <c r="C49" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D49" s="3" t="n"/>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 3 (offset from 8)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1557,7 +1855,11 @@
       <c r="C50" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="D50" s="3" t="n"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="3" t="n"/>
@@ -1576,10 +1878,18 @@
       <c r="C51" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="D51" s="3" t="n"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 80 (offset from 85)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1595,10 +1905,18 @@
       <c r="C52" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="D52" s="3" t="n"/>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E52" s="3" t="n"/>
       <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="n"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 86 (offset from 87)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1614,7 +1932,11 @@
       <c r="C53" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D53" s="3" t="n"/>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
       <c r="G53" s="3" t="n"/>
@@ -1633,10 +1955,18 @@
       <c r="C54" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D54" s="3" t="n"/>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="n"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 17 (offset from 20)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1652,7 +1982,11 @@
       <c r="C55" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="D55" s="3" t="n"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="n"/>
@@ -1671,10 +2005,18 @@
       <c r="C56" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="D56" s="3" t="n"/>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n"/>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 86 (offset from 87)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1690,10 +2032,18 @@
       <c r="C57" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="D57" s="3" t="n"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 83 (offset from 88)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1709,10 +2059,18 @@
       <c r="C58" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="D58" s="3" t="n"/>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
-      <c r="G58" s="3" t="n"/>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 83 (offset from 88)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -1728,7 +2086,11 @@
       <c r="C59" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="D59" s="3" t="n"/>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
       <c r="G59" s="3" t="n"/>
@@ -1747,7 +2109,11 @@
       <c r="C60" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="D60" s="3" t="n"/>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="n"/>
@@ -1766,7 +2132,11 @@
       <c r="C61" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="D61" s="3" t="n"/>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n"/>
       <c r="G61" s="3" t="n"/>
@@ -1785,10 +2155,18 @@
       <c r="C62" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D62" s="3" t="n"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 4 (offset from 7)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1804,7 +2182,11 @@
       <c r="C63" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="D63" s="3" t="n"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E63" s="3" t="n"/>
       <c r="F63" s="3" t="n"/>
       <c r="G63" s="3" t="n"/>
@@ -1823,7 +2205,11 @@
       <c r="C64" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D64" s="3" t="n"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E64" s="3" t="n"/>
       <c r="F64" s="3" t="n"/>
       <c r="G64" s="3" t="n"/>
@@ -1842,10 +2228,18 @@
       <c r="C65" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="D65" s="3" t="n"/>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
-      <c r="G65" s="3" t="n"/>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 24 (offset from 29)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1861,7 +2255,11 @@
       <c r="C66" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="D66" s="3" t="n"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="n"/>
       <c r="G66" s="3" t="n"/>
@@ -1880,7 +2278,11 @@
       <c r="C67" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="D67" s="3" t="n"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
       <c r="G67" s="3" t="n"/>
@@ -1899,7 +2301,11 @@
       <c r="C68" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="D68" s="3" t="n"/>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="3" t="n"/>
@@ -1918,10 +2324,18 @@
       <c r="C69" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="D69" s="3" t="n"/>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="E69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
-      <c r="G69" s="3" t="n"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Found on page 85 (offset from 89)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
